--- a/outputs/evaluation/architecture/validation/CF_M09/CF_M09_arch_eval_avg.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M09/CF_M09_arch_eval_avg.xlsx
@@ -447,10 +447,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7325</v>
+        <v>0.8076</v>
       </c>
       <c r="C2" t="n">
-        <v>0.383</v>
+        <v>0.4375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -465,13 +465,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8104</v>
+        <v>0.8794</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3969</v>
+        <v>0.4496</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9548</v>
+        <v>0.9627</v>
       </c>
     </row>
     <row r="4">
@@ -481,13 +481,13 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="C4" t="n">
         <v>0.3333</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.2667</v>
-      </c>
       <c r="D4" t="n">
-        <v>0.769</v>
+        <v>0.7951</v>
       </c>
     </row>
     <row r="7">
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7402</v>
+        <v>0.79</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -529,10 +529,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6017</v>
+        <v>0.6363</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8089</v>
+        <v>0.8052</v>
       </c>
     </row>
     <row r="10">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6877</v>
+        <v>0.7456</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2013</v>
+        <v>0.1853</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7994</v>
+        <v>0.8741</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3529</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="3">
@@ -660,16 +660,16 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>5.6667</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6667</v>
+        <v>5.3333</v>
       </c>
       <c r="E3" t="n">
-        <v>0.875</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5833</v>
+        <v>0.6667</v>
       </c>
     </row>
     <row r="4">
@@ -685,13 +685,13 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3333</v>
+        <v>1.6667</v>
       </c>
       <c r="E4" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="F4" t="n">
         <v>0.3333</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.2667</v>
       </c>
     </row>
   </sheetData>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24.6667</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.6667</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7325</v>
+        <v>0.8076</v>
       </c>
     </row>
     <row r="9">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.383</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="10">

--- a/outputs/evaluation/architecture/validation/CF_M09/CF_M09_arch_eval_avg.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M09/CF_M09_arch_eval_avg.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,6 +436,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -452,7 +457,10 @@
       <c r="C2" t="n">
         <v>0.4375</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.5664</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -471,6 +479,9 @@
         <v>0.4496</v>
       </c>
       <c r="D3" t="n">
+        <v>0.5934</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9627</v>
       </c>
     </row>
@@ -487,6 +498,9 @@
         <v>0.3333</v>
       </c>
       <c r="D4" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.7951</v>
       </c>
     </row>
